--- a/test/fixtures/key-person.xlsx
+++ b/test/fixtures/key-person.xlsx
@@ -419,12 +419,15 @@
       </c>
       <c r="B2">
         <f>INDIRECT("A"&amp;2)*OFFSET($A$1,0,0)</f>
+        <v>0</v>
       </c>
       <c r="C2">
         <f>IF(A2&gt;1,IF(A2&gt;2,IF(A2&gt;3,IF(A2&gt;4,IF(A2&gt;5,IF(A2&gt;6,IF(A2&gt;7,INDEX($A$2:$A$31,MATCH(A2,$A$2:$A$31,0))+INDEX($A$2:$A$31,MATCH(A2,$A$2:$A$31,0)),0),0),0),0),0),0),0)</f>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>SUM(A2:A2)+1</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -433,12 +436,15 @@
       </c>
       <c r="B3">
         <f>INDIRECT("A"&amp;3)*OFFSET($A$1,1,0)</f>
+        <v>0</v>
       </c>
       <c r="C3">
         <f>IF(A3&gt;1,IF(A3&gt;2,IF(A3&gt;3,IF(A3&gt;4,IF(A3&gt;5,IF(A3&gt;6,IF(A3&gt;7,INDEX($A$2:$A$31,MATCH(A3,$A$2:$A$31,0))+INDEX($A$2:$A$31,MATCH(A3,$A$2:$A$31,0)),0),0),0),0),0),0),0)</f>
+        <v>0</v>
       </c>
       <c r="D3">
         <f>MAX(A2:A3)-2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -447,12 +453,15 @@
       </c>
       <c r="B4">
         <f>INDIRECT("A"&amp;4)*OFFSET($A$1,2,0)</f>
+        <v>0</v>
       </c>
       <c r="C4">
         <f>IF(A4&gt;1,IF(A4&gt;2,IF(A4&gt;3,IF(A4&gt;4,IF(A4&gt;5,IF(A4&gt;6,IF(A4&gt;7,INDEX($A$2:$A$31,MATCH(A4,$A$2:$A$31,0))+INDEX($A$2:$A$31,MATCH(A4,$A$2:$A$31,0)),0),0),0),0),0),0),0)</f>
+        <v>0</v>
       </c>
       <c r="D4">
         <f>MIN(A2:A4)*3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -461,12 +470,15 @@
       </c>
       <c r="B5">
         <f>INDIRECT("A"&amp;5)*OFFSET($A$1,3,0)</f>
+        <v>0</v>
       </c>
       <c r="C5">
         <f>IF(A5&gt;1,IF(A5&gt;2,IF(A5&gt;3,IF(A5&gt;4,IF(A5&gt;5,IF(A5&gt;6,IF(A5&gt;7,INDEX($A$2:$A$31,MATCH(A5,$A$2:$A$31,0))+INDEX($A$2:$A$31,MATCH(A5,$A$2:$A$31,0)),0),0),0),0),0),0),0)</f>
+        <v>0</v>
       </c>
       <c r="D5">
         <f>AVERAGE(A4:A5)/4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -475,9 +487,11 @@
       </c>
       <c r="B6">
         <f>INDIRECT("A"&amp;6)*OFFSET($A$1,4,0)</f>
+        <v>0</v>
       </c>
       <c r="D6">
         <f>SUM(A4:A6)+5</f>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -486,9 +500,11 @@
       </c>
       <c r="B7">
         <f>INDIRECT("A"&amp;7)*OFFSET($A$1,5,0)</f>
+        <v>0</v>
       </c>
       <c r="D7">
         <f>MAX(A4:A7)-6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -497,6 +513,7 @@
       </c>
       <c r="D8">
         <f>MIN(A7:A8)*7</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -505,6 +522,7 @@
       </c>
       <c r="D9">
         <f>AVERAGE(A7:A9)/8</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -513,6 +531,7 @@
       </c>
       <c r="D10">
         <f>SUM(A7:A10)+9</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -521,6 +540,7 @@
       </c>
       <c r="D11">
         <f>MAX(A10:A11)-1</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -529,6 +549,7 @@
       </c>
       <c r="D12">
         <f>MIN(A10:A12)*2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -537,6 +558,7 @@
       </c>
       <c r="D13">
         <f>AVERAGE(A10:A13)/3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -545,6 +567,7 @@
       </c>
       <c r="D14">
         <f>SUM(A13:A14)+4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -553,6 +576,7 @@
       </c>
       <c r="D15">
         <f>MAX(A13:A15)-5</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -561,6 +585,7 @@
       </c>
       <c r="D16">
         <f>MIN(A13:A16)*6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -569,6 +594,7 @@
       </c>
       <c r="D17">
         <f>AVERAGE(A16:A17)/7</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -577,6 +603,7 @@
       </c>
       <c r="D18">
         <f>SUM(A16:A18)+8</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -585,6 +612,7 @@
       </c>
       <c r="D19">
         <f>MAX(A16:A19)-9</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -593,6 +621,7 @@
       </c>
       <c r="D20">
         <f>MIN(A19:A20)*1</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -601,6 +630,7 @@
       </c>
       <c r="D21">
         <f>AVERAGE(A19:A21)/2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -609,6 +639,7 @@
       </c>
       <c r="D22">
         <f>SUM(A19:A22)+3</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -617,6 +648,7 @@
       </c>
       <c r="D23">
         <f>MAX(A22:A23)-4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -625,6 +657,7 @@
       </c>
       <c r="D24">
         <f>MIN(A22:A24)*5</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -633,6 +666,7 @@
       </c>
       <c r="D25">
         <f>AVERAGE(A22:A25)/6</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -641,6 +675,7 @@
       </c>
       <c r="D26">
         <f>SUM(A25:A26)+7</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -649,6 +684,7 @@
       </c>
       <c r="D27">
         <f>MAX(A25:A27)-8</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -657,6 +693,7 @@
       </c>
       <c r="D28">
         <f>MIN(A25:A28)*9</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -665,6 +702,7 @@
       </c>
       <c r="D29">
         <f>AVERAGE(A28:A29)/1</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -673,6 +711,7 @@
       </c>
       <c r="D30">
         <f>SUM(A28:A30)+2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -681,6 +720,7 @@
       </c>
       <c r="D31">
         <f>MAX(A28:A31)-3</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
